--- a/artfynd/A 61826-2025 artfynd.xlsx
+++ b/artfynd/A 61826-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130259862</v>
+        <v>130352517</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621326</v>
+        <v>621779</v>
       </c>
       <c r="R2" t="n">
-        <v>6895656</v>
+        <v>6895807</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130260702</v>
+        <v>130260027</v>
       </c>
       <c r="B3" t="n">
-        <v>79251</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621413</v>
+        <v>621416</v>
       </c>
       <c r="R3" t="n">
-        <v>6895716</v>
+        <v>6895629</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spridd på en stor mängd träd i närområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130260027</v>
+        <v>130260702</v>
       </c>
       <c r="B4" t="n">
-        <v>79251</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621416</v>
+        <v>621413</v>
       </c>
       <c r="R4" t="n">
-        <v>6895629</v>
+        <v>6895716</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spridd på en stor mängd träd i närområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130260134</v>
+        <v>130352490</v>
       </c>
       <c r="B5" t="n">
-        <v>80353</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621478</v>
+        <v>621038</v>
       </c>
       <c r="R5" t="n">
-        <v>6895674</v>
+        <v>6895835</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1041,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130260666</v>
+        <v>130352492</v>
       </c>
       <c r="B6" t="n">
-        <v>78226</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,34 +1079,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621438</v>
+        <v>621016</v>
       </c>
       <c r="R6" t="n">
-        <v>6895723</v>
+        <v>6895870</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1138,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130260622</v>
+        <v>130352496</v>
       </c>
       <c r="B7" t="n">
-        <v>78226</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,34 +1176,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621463</v>
+        <v>621085</v>
       </c>
       <c r="R7" t="n">
-        <v>6895702</v>
+        <v>6895811</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1235,12 +1230,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130260689</v>
+        <v>130352501</v>
       </c>
       <c r="B8" t="n">
-        <v>91774</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1273,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621434</v>
+        <v>621124</v>
       </c>
       <c r="R8" t="n">
-        <v>6895717</v>
+        <v>6895839</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1332,12 +1327,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,50 +1359,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130259884</v>
+        <v>130352507</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>80305</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621326</v>
+        <v>621150</v>
       </c>
       <c r="R9" t="n">
-        <v>6895657</v>
+        <v>6895773</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1434,12 +1427,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1448,6 +1441,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1466,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130260235</v>
+        <v>130352491</v>
       </c>
       <c r="B10" t="n">
-        <v>78226</v>
+        <v>89292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,37 +1471,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621523</v>
+        <v>621030</v>
       </c>
       <c r="R10" t="n">
-        <v>6895666</v>
+        <v>6895843</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1534,17 +1525,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På torraka</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1553,7 +1539,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1572,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130260224</v>
+        <v>130352494</v>
       </c>
       <c r="B11" t="n">
-        <v>79809</v>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,34 +1568,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621526</v>
+        <v>621086</v>
       </c>
       <c r="R11" t="n">
-        <v>6895669</v>
+        <v>6895831</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1637,12 +1622,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1669,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130260894</v>
+        <v>130352499</v>
       </c>
       <c r="B12" t="n">
-        <v>79219</v>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,34 +1665,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vargberget, Vargberget, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621144</v>
+        <v>621116</v>
       </c>
       <c r="R12" t="n">
-        <v>6895798</v>
+        <v>6895835</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1734,12 +1719,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1766,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130352489</v>
+        <v>130260689</v>
       </c>
       <c r="B13" t="n">
-        <v>57864</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,42 +1762,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621034</v>
+        <v>621434</v>
       </c>
       <c r="R13" t="n">
-        <v>6895835</v>
+        <v>6895717</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1836,12 +1816,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1868,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130352498</v>
+        <v>130263790</v>
       </c>
       <c r="B14" t="n">
-        <v>91776</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621119</v>
+        <v>621116</v>
       </c>
       <c r="R14" t="n">
-        <v>6895842</v>
+        <v>6895813</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1933,12 +1913,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1965,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130352509</v>
+        <v>130352497</v>
       </c>
       <c r="B15" t="n">
-        <v>79840</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2000,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621416</v>
+        <v>621099</v>
       </c>
       <c r="R15" t="n">
-        <v>6895623</v>
+        <v>6895812</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2062,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130263786</v>
+        <v>130352498</v>
       </c>
       <c r="B16" t="n">
-        <v>57864</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2073,42 +2053,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621421</v>
+        <v>621119</v>
       </c>
       <c r="R16" t="n">
-        <v>6895588</v>
+        <v>6895842</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2132,17 +2107,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2169,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130352492</v>
+        <v>130352510</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2180,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2204,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621016</v>
+        <v>621421</v>
       </c>
       <c r="R17" t="n">
-        <v>6895870</v>
+        <v>6895625</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2266,53 +2236,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130263788</v>
+        <v>130352500</v>
       </c>
       <c r="B18" t="n">
-        <v>57864</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621516</v>
+        <v>621117</v>
       </c>
       <c r="R18" t="n">
-        <v>6895684</v>
+        <v>6895836</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2336,12 +2301,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2368,53 +2333,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130263787</v>
+        <v>130260894</v>
       </c>
       <c r="B19" t="n">
-        <v>57864</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Vargberget, Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621561</v>
+        <v>621144</v>
       </c>
       <c r="R19" t="n">
-        <v>6895717</v>
+        <v>6895798</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2470,32 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130352512</v>
+        <v>130352495</v>
       </c>
       <c r="B20" t="n">
-        <v>78228</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2505,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621759</v>
+        <v>621079</v>
       </c>
       <c r="R20" t="n">
-        <v>6895760</v>
+        <v>6895806</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2567,10 +2527,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130352517</v>
+        <v>130352502</v>
       </c>
       <c r="B21" t="n">
-        <v>92049</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,21 +2538,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2602,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621779</v>
+        <v>621118</v>
       </c>
       <c r="R21" t="n">
-        <v>6895807</v>
+        <v>6895824</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2664,10 +2624,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130352490</v>
+        <v>130352509</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2675,21 +2635,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2699,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>621038</v>
+        <v>621416</v>
       </c>
       <c r="R22" t="n">
-        <v>6895835</v>
+        <v>6895623</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2761,10 +2721,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130352497</v>
+        <v>130352516</v>
       </c>
       <c r="B23" t="n">
-        <v>91776</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,21 +2732,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2796,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>621099</v>
+        <v>621781</v>
       </c>
       <c r="R23" t="n">
-        <v>6895812</v>
+        <v>6895805</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2858,10 +2818,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130263789</v>
+        <v>130352506</v>
       </c>
       <c r="B24" t="n">
-        <v>57864</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,42 +2829,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>621148</v>
+        <v>621150</v>
       </c>
       <c r="R24" t="n">
-        <v>6895788</v>
+        <v>6895773</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2928,12 +2883,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2960,45 +2915,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130352499</v>
+        <v>130260134</v>
       </c>
       <c r="B25" t="n">
-        <v>92074</v>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621116</v>
+        <v>621478</v>
       </c>
       <c r="R25" t="n">
-        <v>6895835</v>
+        <v>6895674</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3025,12 +2980,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3057,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130352506</v>
+        <v>130260235</v>
       </c>
       <c r="B26" t="n">
-        <v>80326</v>
+        <v>78334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3068,34 +3023,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621150</v>
+        <v>621523</v>
       </c>
       <c r="R26" t="n">
-        <v>6895773</v>
+        <v>6895666</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3122,12 +3080,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På torraka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3136,6 +3099,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3154,50 +3118,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130352508</v>
+        <v>130260622</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>78334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>621324</v>
+        <v>621463</v>
       </c>
       <c r="R27" t="n">
-        <v>6895657</v>
+        <v>6895702</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3224,12 +3183,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3256,45 +3215,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130352503</v>
+        <v>130260666</v>
       </c>
       <c r="B28" t="n">
-        <v>5177</v>
+        <v>78334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>621140</v>
+        <v>621438</v>
       </c>
       <c r="R28" t="n">
-        <v>6895804</v>
+        <v>6895723</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3321,12 +3280,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3353,10 +3312,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130352495</v>
+        <v>130352512</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>78334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3364,21 +3323,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>621079</v>
+        <v>621759</v>
       </c>
       <c r="R29" t="n">
-        <v>6895806</v>
+        <v>6895760</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3450,10 +3409,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130352494</v>
+        <v>130352514</v>
       </c>
       <c r="B30" t="n">
-        <v>92074</v>
+        <v>78334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3461,21 +3420,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6487</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3485,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>621086</v>
+        <v>621768</v>
       </c>
       <c r="R30" t="n">
-        <v>6895831</v>
+        <v>6895791</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3547,10 +3506,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130263790</v>
+        <v>130263785</v>
       </c>
       <c r="B31" t="n">
-        <v>91776</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,37 +3517,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>621116</v>
+        <v>621315</v>
       </c>
       <c r="R31" t="n">
-        <v>6895813</v>
+        <v>6895655</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3644,10 +3608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130352518</v>
+        <v>130263786</v>
       </c>
       <c r="B32" t="n">
-        <v>79811</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,40 +3619,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>621754</v>
+        <v>621421</v>
       </c>
       <c r="R32" t="n">
-        <v>6895822</v>
+        <v>6895588</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3712,12 +3678,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3726,7 +3697,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3745,10 +3715,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130352514</v>
+        <v>130263787</v>
       </c>
       <c r="B33" t="n">
-        <v>78228</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3756,37 +3726,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>621768</v>
+        <v>621561</v>
       </c>
       <c r="R33" t="n">
-        <v>6895791</v>
+        <v>6895717</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3810,12 +3785,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3842,10 +3817,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130352491</v>
+        <v>130263788</v>
       </c>
       <c r="B34" t="n">
-        <v>89169</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3853,37 +3828,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>621030</v>
+        <v>621516</v>
       </c>
       <c r="R34" t="n">
-        <v>6895843</v>
+        <v>6895684</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3907,12 +3887,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3939,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130352513</v>
+        <v>130263789</v>
       </c>
       <c r="B35" t="n">
-        <v>79811</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3950,37 +3930,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>621763</v>
+        <v>621148</v>
       </c>
       <c r="R35" t="n">
-        <v>6895764</v>
+        <v>6895788</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4004,12 +3989,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4036,10 +4021,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130263785</v>
+        <v>130352489</v>
       </c>
       <c r="B36" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4067,7 +4052,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4076,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>621315</v>
+        <v>621034</v>
       </c>
       <c r="R36" t="n">
-        <v>6895655</v>
+        <v>6895835</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4106,12 +4091,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4138,10 +4123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130352516</v>
+        <v>130352519</v>
       </c>
       <c r="B37" t="n">
-        <v>79840</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4149,37 +4134,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>621781</v>
+        <v>621382</v>
       </c>
       <c r="R37" t="n">
-        <v>6895805</v>
+        <v>6895667</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4235,10 +4224,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130352500</v>
+        <v>130259862</v>
       </c>
       <c r="B38" t="n">
-        <v>91739</v>
+        <v>5179</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4246,34 +4235,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621117</v>
+        <v>621326</v>
       </c>
       <c r="R38" t="n">
-        <v>6895836</v>
+        <v>6895656</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4300,12 +4294,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4332,32 +4326,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352515</v>
+        <v>130352503</v>
       </c>
       <c r="B39" t="n">
-        <v>79811</v>
+        <v>5179</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4367,10 +4361,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621768</v>
+        <v>621140</v>
       </c>
       <c r="R39" t="n">
-        <v>6895793</v>
+        <v>6895804</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4429,32 +4423,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130352502</v>
+        <v>130352505</v>
       </c>
       <c r="B40" t="n">
-        <v>79221</v>
+        <v>58327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4464,10 +4458,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621118</v>
+        <v>621121</v>
       </c>
       <c r="R40" t="n">
-        <v>6895824</v>
+        <v>6895806</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4526,45 +4520,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130352496</v>
+        <v>130259884</v>
       </c>
       <c r="B41" t="n">
-        <v>79253</v>
+        <v>5199</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>621085</v>
+        <v>621326</v>
       </c>
       <c r="R41" t="n">
-        <v>6895811</v>
+        <v>6895657</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4591,12 +4590,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4623,10 +4622,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130352505</v>
+        <v>130352508</v>
       </c>
       <c r="B42" t="n">
-        <v>58236</v>
+        <v>5199</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4634,16 +4633,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4652,16 +4651,21 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>621121</v>
+        <v>621324</v>
       </c>
       <c r="R42" t="n">
-        <v>6895806</v>
+        <v>6895657</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4720,32 +4724,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130352510</v>
+        <v>130352493</v>
       </c>
       <c r="B43" t="n">
-        <v>91797</v>
+        <v>80392</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4755,10 +4759,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>621421</v>
+        <v>621073</v>
       </c>
       <c r="R43" t="n">
-        <v>6895625</v>
+        <v>6895860</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4817,10 +4821,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130352511</v>
+        <v>130260224</v>
       </c>
       <c r="B44" t="n">
-        <v>79811</v>
+        <v>79917</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4848,14 +4852,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>621627</v>
+        <v>621526</v>
       </c>
       <c r="R44" t="n">
-        <v>6895655</v>
+        <v>6895669</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4882,12 +4886,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4914,10 +4918,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130352519</v>
+        <v>130352511</v>
       </c>
       <c r="B45" t="n">
-        <v>57864</v>
+        <v>79917</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4925,41 +4929,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>621382</v>
+        <v>621627</v>
       </c>
       <c r="R45" t="n">
-        <v>6895667</v>
+        <v>6895655</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5015,32 +5015,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130352493</v>
+        <v>130352513</v>
       </c>
       <c r="B46" t="n">
-        <v>80286</v>
+        <v>79917</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5050,10 +5050,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>621073</v>
+        <v>621763</v>
       </c>
       <c r="R46" t="n">
-        <v>6895860</v>
+        <v>6895764</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5112,48 +5112,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130352507</v>
+        <v>130352515</v>
       </c>
       <c r="B47" t="n">
-        <v>80199</v>
+        <v>79917</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>392</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>621150</v>
+        <v>621768</v>
       </c>
       <c r="R47" t="n">
-        <v>6895773</v>
+        <v>6895793</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5194,7 +5191,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5210,6 +5206,107 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130352518</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>621754</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6895822</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61826-2025 artfynd.xlsx
+++ b/artfynd/A 61826-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130260027</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130260702</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352490</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352492</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352496</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352501</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352507</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352491</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352494</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352499</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130260689</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263790</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352497</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352498</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +2211,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352510</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2233,6 +2313,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352500</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130260894</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352495</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352502</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352509</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352506</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130260134</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2921,6 +3036,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130260235</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3018,6 +3138,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130260622</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3115,6 +3240,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130260666</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3217,6 +3347,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263785</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3324,6 +3459,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263786</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3426,6 +3566,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263787</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3528,6 +3673,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263788</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3630,6 +3780,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263789</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3732,6 +3887,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352489</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3833,6 +3993,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352519</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3935,6 +4100,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130259862</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4032,6 +4202,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352503</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4129,6 +4304,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352505</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4231,6 +4411,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130259884</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4333,6 +4518,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352508</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4430,6 +4620,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352493</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4527,6 +4722,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130260224</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4624,6 +4824,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352517</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4721,6 +4926,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352516</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4818,6 +5028,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352512</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4915,6 +5130,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352514</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5012,6 +5232,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352511</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5109,6 +5334,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352513</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5206,6 +5436,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352515</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5307,8 +5542,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130352518</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>